--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SESE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SESE.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>33.9672</v>
+        <v>34.5242</v>
       </c>
       <c r="E2" t="n">
-        <v>35.3918</v>
+        <v>28.7755</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.424300000000001</v>
+        <v>5.748799999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.7477</v>
+        <v>19.5181</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.740499999999999</v>
+        <v>8.0946</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.007299999999999</v>
+        <v>11.4237</v>
       </c>
       <c r="J2" t="n">
-        <v>18.9059</v>
+        <v>53.3553</v>
       </c>
       <c r="K2" t="n">
-        <v>11.5463</v>
+        <v>31.6626</v>
       </c>
       <c r="L2" t="n">
-        <v>7.3598</v>
+        <v>21.6927</v>
       </c>
       <c r="M2" t="n">
-        <v>-26.6536</v>
+        <v>-33.8371</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.2867</v>
+        <v>-23.568</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.3672</v>
+        <v>-10.2687</v>
       </c>
       <c r="P2" t="n">
-        <v>11.9159</v>
+        <v>4.4927</v>
       </c>
       <c r="Q2" t="n">
-        <v>-29.8873</v>
+        <v>-53.9142</v>
       </c>
       <c r="R2" t="n">
-        <v>41.8036</v>
+        <v>58.4077</v>
       </c>
       <c r="S2" t="n">
-        <v>16.4164</v>
+        <v>-1.1544</v>
       </c>
       <c r="T2" t="n">
-        <v>8.369999999999999</v>
+        <v>-2.6905</v>
       </c>
       <c r="U2" t="n">
-        <v>8.0465</v>
+        <v>1.5358</v>
       </c>
       <c r="V2" t="n">
-        <v>13.383</v>
+        <v>11.6677</v>
       </c>
       <c r="W2" t="n">
-        <v>38.0028</v>
+        <v>32.0254</v>
       </c>
       <c r="X2" t="n">
-        <v>-24.6199</v>
+        <v>-20.3575</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>26.3662</v>
+        <v>27.1698</v>
       </c>
       <c r="E3" t="n">
-        <v>22.653</v>
+        <v>22.4301</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7132</v>
+        <v>4.7397</v>
       </c>
       <c r="G3" t="n">
         <v>13.0843</v>
@@ -688,13 +688,13 @@
         <v>18.5576</v>
       </c>
       <c r="S3" t="n">
-        <v>3.78</v>
+        <v>4.5837</v>
       </c>
       <c r="T3" t="n">
-        <v>4.8328</v>
+        <v>4.6097</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0525</v>
+        <v>-0.02580000000000018</v>
       </c>
       <c r="V3" t="n">
         <v>-1.8281</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>24.9899</v>
+        <v>23.7228</v>
       </c>
       <c r="E4" t="n">
-        <v>19.4958</v>
+        <v>28.7561</v>
       </c>
       <c r="F4" t="n">
-        <v>5.493799999999999</v>
+        <v>-5.0329</v>
       </c>
       <c r="G4" t="n">
-        <v>19.5181</v>
+        <v>-7.7477</v>
       </c>
       <c r="H4" t="n">
-        <v>8.0946</v>
+        <v>-1.740499999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>11.4237</v>
+        <v>-6.007299999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>53.3553</v>
+        <v>18.9059</v>
       </c>
       <c r="K4" t="n">
-        <v>31.6626</v>
+        <v>11.5463</v>
       </c>
       <c r="L4" t="n">
-        <v>21.6927</v>
+        <v>7.3598</v>
       </c>
       <c r="M4" t="n">
-        <v>-33.8371</v>
+        <v>-26.6536</v>
       </c>
       <c r="N4" t="n">
-        <v>-23.568</v>
+        <v>-13.2867</v>
       </c>
       <c r="O4" t="n">
-        <v>-10.2687</v>
+        <v>-13.3672</v>
       </c>
       <c r="P4" t="n">
-        <v>4.4927</v>
+        <v>11.9159</v>
       </c>
       <c r="Q4" t="n">
-        <v>-53.9142</v>
+        <v>-29.8873</v>
       </c>
       <c r="R4" t="n">
-        <v>58.4077</v>
+        <v>41.8036</v>
       </c>
       <c r="S4" t="n">
-        <v>-10.6889</v>
+        <v>6.1718</v>
       </c>
       <c r="T4" t="n">
-        <v>-11.9699</v>
+        <v>1.7344</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2811</v>
+        <v>4.4376</v>
       </c>
       <c r="V4" t="n">
-        <v>11.6677</v>
+        <v>13.383</v>
       </c>
       <c r="W4" t="n">
-        <v>32.0254</v>
+        <v>38.0028</v>
       </c>
       <c r="X4" t="n">
-        <v>-20.3575</v>
+        <v>-24.6199</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>13.5492</v>
+        <v>3.281499999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>13.8578</v>
+        <v>1.4312</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3091000000000017</v>
+        <v>1.8501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8704999999999994</v>
+        <v>8.2056</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7384</v>
+        <v>6.1058</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.867999999999999</v>
+        <v>2.0997</v>
       </c>
       <c r="J5" t="n">
-        <v>23.4547</v>
+        <v>12.3404</v>
       </c>
       <c r="K5" t="n">
-        <v>14.1733</v>
+        <v>10.9082</v>
       </c>
       <c r="L5" t="n">
-        <v>9.2814</v>
+        <v>1.4322</v>
       </c>
       <c r="M5" t="n">
-        <v>-22.5845</v>
+        <v>-4.135000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.4349</v>
+        <v>-4.8023</v>
       </c>
       <c r="O5" t="n">
-        <v>-12.1492</v>
+        <v>0.6676000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9301</v>
+        <v>4.883599999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-33.4033</v>
+        <v>-11.33</v>
       </c>
       <c r="R5" t="n">
-        <v>36.3337</v>
+        <v>16.2136</v>
       </c>
       <c r="S5" t="n">
-        <v>21.2745</v>
+        <v>-3.3389</v>
       </c>
       <c r="T5" t="n">
-        <v>14.1004</v>
+        <v>-0.1363999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>7.1739</v>
+        <v>-3.2023</v>
       </c>
       <c r="V5" t="n">
-        <v>-11.5258</v>
+        <v>-6.468500000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>9.7059</v>
+        <v>0.5572999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-21.2318</v>
+        <v>-7.026</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>2.625500000000001</v>
+        <v>1.605299999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>1.327899999999999</v>
+        <v>0.4352000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2978</v>
+        <v>1.169700000000001</v>
       </c>
       <c r="G6" t="n">
         <v>8.5159</v>
@@ -922,13 +922,13 @@
         <v>56.0633</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1152</v>
+        <v>1.0947</v>
       </c>
       <c r="T6" t="n">
-        <v>3.6109</v>
+        <v>2.7188</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.4961</v>
+        <v>-1.6237</v>
       </c>
       <c r="V6" t="n">
         <v>-9.372599999999998</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0252</v>
+        <v>1.4752</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0681</v>
+        <v>4.2705</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9570000000000002</v>
+        <v>-2.7955</v>
       </c>
       <c r="G7" t="n">
-        <v>8.2056</v>
+        <v>0.8704999999999994</v>
       </c>
       <c r="H7" t="n">
-        <v>6.1058</v>
+        <v>3.7384</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0997</v>
+        <v>-2.867999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>12.3404</v>
+        <v>23.4547</v>
       </c>
       <c r="K7" t="n">
-        <v>10.9082</v>
+        <v>14.1733</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4322</v>
+        <v>9.2814</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.135000000000001</v>
+        <v>-22.5845</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.8023</v>
+        <v>-10.4349</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6676000000000001</v>
+        <v>-12.1492</v>
       </c>
       <c r="P7" t="n">
-        <v>4.883599999999999</v>
+        <v>2.9301</v>
       </c>
       <c r="Q7" t="n">
-        <v>-11.33</v>
+        <v>-33.4033</v>
       </c>
       <c r="R7" t="n">
-        <v>16.2136</v>
+        <v>36.3337</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.595400000000001</v>
+        <v>9.2005</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4994000000000001</v>
+        <v>4.5131</v>
       </c>
       <c r="U7" t="n">
-        <v>-4.0956</v>
+        <v>4.6875</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.468500000000001</v>
+        <v>-11.5258</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5572999999999999</v>
+        <v>9.7059</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.026</v>
+        <v>-21.2318</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. SUÑOL CUBARSI</t>
+          <t>P. REGUANT MAJEM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0002000000000000057</v>
+        <v>0.2349</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0605</v>
+        <v>0.0732</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06030000000000001</v>
+        <v>0.1616</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.135</v>
+        <v>-2.535</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.1215</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.135</v>
+        <v>-2.6565</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-1.9204</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.0614</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.9818</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.135</v>
+        <v>-0.6146</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.0601</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.135</v>
+        <v>-0.6747</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0605</v>
+        <v>-0.5152</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0605</v>
+        <v>-0.4436</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.0716</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.5037</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. REGUANT MAJEM</t>
+          <t>P. SUÑOL CUBARSI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0297</v>
+        <v>0.202</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0279</v>
+        <v>0.1417</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0018</v>
+        <v>0.06030000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.535</v>
+        <v>-0.135</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1215</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6565</v>
+        <v>-0.135</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9204</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9818</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6146</v>
+        <v>-0.135</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0601</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6747</v>
+        <v>-0.135</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7796999999999999</v>
+        <v>0.1417</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5447</v>
+        <v>0.1417</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.235</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2.5037</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GARCIA RODRIGUEZ</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2757</v>
+        <v>-0.6711999999999998</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2879</v>
+        <v>-10.5883</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01230000000000001</v>
+        <v>9.9171</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6836</v>
+        <v>4.438599999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9823</v>
+        <v>5.2087</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7013</v>
+        <v>-0.7701000000000002</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9246</v>
+        <v>5.1631</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8978999999999999</v>
+        <v>5.3901</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.02660000000000007</v>
+        <v>-0.2270000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7591</v>
+        <v>-0.7246000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0844</v>
+        <v>-0.1814999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6747</v>
+        <v>-0.5429000000000002</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1954</v>
+        <v>-6.837</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-17.9714</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7813</v>
+        <v>11.1345</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6153</v>
+        <v>0.676</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6052</v>
+        <v>1.0015</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.01</v>
+        <v>-0.3254</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2186</v>
+        <v>1.0511</v>
       </c>
       <c r="W10" t="n">
         <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ QUILEZ</t>
+          <t>P. GARCIA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,67 +1264,67 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3423</v>
+        <v>-0.7987000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6244000000000001</v>
+        <v>-0.7823</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7178</v>
+        <v>-0.0164</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2565</v>
+        <v>-1.6836</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6224</v>
+        <v>-0.9823</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.634</v>
+        <v>-0.7013</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1019</v>
+        <v>-0.9246</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0614</v>
+        <v>-0.8978999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0405</v>
+        <v>-0.02660000000000007</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3583</v>
+        <v>-0.7591</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6838</v>
+        <v>-0.0844</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6745</v>
+        <v>-0.6747</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3675</v>
+        <v>-0.1954</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5859</v>
+        <v>0.7813</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2816</v>
+        <v>-0.1383</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2272</v>
+        <v>-0.09960000000000002</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0545</v>
+        <v>-0.0386</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.47</v>
+        <v>-1.1861</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5698</v>
+        <v>-1.3676</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0998</v>
+        <v>0.1815</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5326</v>
@@ -1390,13 +1390,13 @@
         <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1876</v>
+        <v>0.0963</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2421</v>
+        <v>-0.0399</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0545</v>
+        <v>0.1362</v>
       </c>
       <c r="V12" t="n">
         <v>0.0549</v>
@@ -1423,13 +1423,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8464</v>
+        <v>-1.7211</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1259000000000001</v>
+        <v>0.3886000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9723</v>
+        <v>-2.1097</v>
       </c>
       <c r="G13" t="n">
         <v>-2.6259</v>
@@ -1468,13 +1468,13 @@
         <v>3.3208</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7950999999999999</v>
+        <v>-0.6698999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9103</v>
+        <v>-0.6476</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1153</v>
+        <v>-0.02229999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5507</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>A. FERNANDEZ QUILEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.783899999999999</v>
+        <v>-2.0695</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.4791</v>
+        <v>-1.4333</v>
       </c>
       <c r="F14" t="n">
-        <v>8.695499999999999</v>
+        <v>-0.6361</v>
       </c>
       <c r="G14" t="n">
-        <v>4.438599999999999</v>
+        <v>-1.2565</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2087</v>
+        <v>-0.6224</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7701000000000002</v>
+        <v>-0.634</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1631</v>
+        <v>0.1019</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3901</v>
+        <v>0.0614</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2270000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7246000000000001</v>
+        <v>-1.3583</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1814999999999999</v>
+        <v>-0.6838</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5429000000000002</v>
+        <v>-0.6745</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.837</v>
+        <v>-1.3675</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.9714</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>11.1345</v>
+        <v>0.5859</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.4364</v>
+        <v>0.5545</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.8895</v>
+        <v>0.4183</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5468</v>
+        <v>0.1362</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0511</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.2743</v>
+        <v>-3.9434</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.6651</v>
+        <v>-2.7958</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6092</v>
+        <v>-1.1477</v>
       </c>
       <c r="G15" t="n">
         <v>-6.5025</v>
@@ -1624,13 +1624,13 @@
         <v>4.1021</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6667</v>
+        <v>-0.3357</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5706</v>
+        <v>-0.7012</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.09600000000000003</v>
+        <v>0.3656</v>
       </c>
       <c r="V15" t="n">
         <v>0.9414</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-11.6128</v>
+        <v>-5.912400000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-11.6296</v>
+        <v>-8.779900000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01700000000000079</v>
+        <v>2.8672</v>
       </c>
       <c r="G16" t="n">
         <v>-3.464</v>
@@ -1702,13 +1702,13 @@
         <v>35.357</v>
       </c>
       <c r="S16" t="n">
-        <v>-7.6402</v>
+        <v>-1.9404</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.1081</v>
+        <v>-1.2583</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.5322</v>
+        <v>-0.6819999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-12.0338</v>
@@ -1735,13 +1735,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>-19.5555</v>
+        <v>-10.0372</v>
       </c>
       <c r="E17" t="n">
-        <v>-9.1934</v>
+        <v>-2.500699999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-10.3621</v>
+        <v>-7.5364</v>
       </c>
       <c r="G17" t="n">
         <v>-3.5132</v>
@@ -1780,13 +1780,13 @@
         <v>23.441</v>
       </c>
       <c r="S17" t="n">
-        <v>-13.4418</v>
+        <v>-3.9234</v>
       </c>
       <c r="T17" t="n">
-        <v>-8.013200000000001</v>
+        <v>-1.3205</v>
       </c>
       <c r="U17" t="n">
-        <v>-5.4285</v>
+        <v>-2.6028</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2563</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-21.231</v>
+        <v>-13.8213</v>
       </c>
       <c r="E18" t="n">
-        <v>-26.327</v>
+        <v>0.07939999999999992</v>
       </c>
       <c r="F18" t="n">
-        <v>5.095699999999999</v>
+        <v>-13.9007</v>
       </c>
       <c r="G18" t="n">
-        <v>-15.8716</v>
+        <v>-20.6737</v>
       </c>
       <c r="H18" t="n">
-        <v>-12.2053</v>
+        <v>-7.3278</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.666099999999999</v>
+        <v>-13.3455</v>
       </c>
       <c r="J18" t="n">
-        <v>8.053799999999999</v>
+        <v>8.5871</v>
       </c>
       <c r="K18" t="n">
-        <v>2.939700000000001</v>
+        <v>12.4787</v>
       </c>
       <c r="L18" t="n">
-        <v>5.1146</v>
+        <v>-3.8917</v>
       </c>
       <c r="M18" t="n">
-        <v>-23.9259</v>
+        <v>-29.2609</v>
       </c>
       <c r="N18" t="n">
-        <v>-15.145</v>
+        <v>-19.8066</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.7806</v>
+        <v>-9.454000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.665000000000001</v>
+        <v>19.7297</v>
       </c>
       <c r="Q18" t="n">
-        <v>-48.2496</v>
+        <v>-26.3713</v>
       </c>
       <c r="R18" t="n">
-        <v>42.5846</v>
+        <v>46.1009</v>
       </c>
       <c r="S18" t="n">
-        <v>4.8632</v>
+        <v>-2.0519</v>
       </c>
       <c r="T18" t="n">
-        <v>7.492500000000001</v>
+        <v>0.2452</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.6293</v>
+        <v>-2.2971</v>
       </c>
       <c r="V18" t="n">
-        <v>-4.5577</v>
+        <v>-10.8255</v>
       </c>
       <c r="W18" t="n">
-        <v>6.375999999999999</v>
+        <v>17.618</v>
       </c>
       <c r="X18" t="n">
-        <v>-10.934</v>
+        <v>-28.444</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-24.0262</v>
+        <v>-16.371</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.561299999999999</v>
+        <v>-22.0574</v>
       </c>
       <c r="F19" t="n">
-        <v>-18.4656</v>
+        <v>5.686</v>
       </c>
       <c r="G19" t="n">
-        <v>-20.6737</v>
+        <v>-33.526</v>
       </c>
       <c r="H19" t="n">
-        <v>-7.3278</v>
+        <v>-13.2201</v>
       </c>
       <c r="I19" t="n">
-        <v>-13.3455</v>
+        <v>-20.3054</v>
       </c>
       <c r="J19" t="n">
-        <v>8.5871</v>
+        <v>5.7826</v>
       </c>
       <c r="K19" t="n">
-        <v>12.4787</v>
+        <v>8.535299999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.8917</v>
+        <v>-2.752500000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-29.2609</v>
+        <v>-39.3082</v>
       </c>
       <c r="N19" t="n">
-        <v>-19.8066</v>
+        <v>-21.7553</v>
       </c>
       <c r="O19" t="n">
-        <v>-9.454000000000001</v>
+        <v>-17.5532</v>
       </c>
       <c r="P19" t="n">
-        <v>19.7297</v>
+        <v>15.2369</v>
       </c>
       <c r="Q19" t="n">
-        <v>-26.3713</v>
+        <v>-43.9519</v>
       </c>
       <c r="R19" t="n">
-        <v>46.1009</v>
+        <v>59.1889</v>
       </c>
       <c r="S19" t="n">
-        <v>-12.2569</v>
+        <v>-0.1506999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-5.3953</v>
+        <v>-0.1226</v>
       </c>
       <c r="U19" t="n">
-        <v>-6.8618</v>
+        <v>-0.02800000000000011</v>
       </c>
       <c r="V19" t="n">
-        <v>-10.8255</v>
+        <v>2.0689</v>
       </c>
       <c r="W19" t="n">
-        <v>17.618</v>
+        <v>16.2347</v>
       </c>
       <c r="X19" t="n">
-        <v>-28.444</v>
+        <v>-14.1664</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D20" t="n">
-        <v>-26.0026</v>
+        <v>-28.6561</v>
       </c>
       <c r="E20" t="n">
-        <v>-25.7963</v>
+        <v>-33.305</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2062000000000004</v>
+        <v>4.6493</v>
       </c>
       <c r="G20" t="n">
-        <v>-33.526</v>
+        <v>-15.8716</v>
       </c>
       <c r="H20" t="n">
-        <v>-13.2201</v>
+        <v>-12.2053</v>
       </c>
       <c r="I20" t="n">
-        <v>-20.3054</v>
+        <v>-3.666099999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>5.7826</v>
+        <v>8.053799999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>8.535299999999999</v>
+        <v>2.939700000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.752500000000001</v>
+        <v>5.1146</v>
       </c>
       <c r="M20" t="n">
-        <v>-39.3082</v>
+        <v>-23.9259</v>
       </c>
       <c r="N20" t="n">
-        <v>-21.7553</v>
+        <v>-15.145</v>
       </c>
       <c r="O20" t="n">
-        <v>-17.5532</v>
+        <v>-8.7806</v>
       </c>
       <c r="P20" t="n">
-        <v>15.2369</v>
+        <v>-5.665000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-43.9519</v>
+        <v>-48.2496</v>
       </c>
       <c r="R20" t="n">
-        <v>59.1889</v>
+        <v>42.5846</v>
       </c>
       <c r="S20" t="n">
-        <v>-9.7821</v>
+        <v>-2.562</v>
       </c>
       <c r="T20" t="n">
-        <v>-3.8615</v>
+        <v>0.5141</v>
       </c>
       <c r="U20" t="n">
-        <v>-5.9204</v>
+        <v>-3.0758</v>
       </c>
       <c r="V20" t="n">
-        <v>2.0689</v>
+        <v>-4.5577</v>
       </c>
       <c r="W20" t="n">
-        <v>16.2347</v>
+        <v>6.375999999999999</v>
       </c>
       <c r="X20" t="n">
-        <v>-14.1664</v>
+        <v>-10.934</v>
       </c>
     </row>
     <row r="21">
@@ -2047,16 +2047,16 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-14.9274</v>
+        <v>7.027700000000003</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.301999999999985</v>
+        <v>3.171200000000013</v>
       </c>
       <c r="F21" t="n">
-        <v>-9.626000000000007</v>
+        <v>3.8559</v>
       </c>
       <c r="G21" t="n">
-        <v>-46.43429999999999</v>
+        <v>-46.4343</v>
       </c>
       <c r="H21" t="n">
         <v>10.2002</v>
@@ -2071,7 +2071,7 @@
         <v>175.6902</v>
       </c>
       <c r="L21" t="n">
-        <v>44.6706</v>
+        <v>44.67060000000001</v>
       </c>
       <c r="M21" t="n">
         <v>-266.7957</v>
@@ -2092,16 +2092,16 @@
         <v>455.1485</v>
       </c>
       <c r="S21" t="n">
-        <v>-16.2157</v>
+        <v>5.738400000000003</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.03650000000000153</v>
+        <v>8.436600000000002</v>
       </c>
       <c r="U21" t="n">
-        <v>-16.1784</v>
+        <v>-2.696500000000002</v>
       </c>
       <c r="V21" t="n">
-        <v>-25.5297</v>
+        <v>-25.52970000000001</v>
       </c>
       <c r="W21" t="n">
         <v>156.2676</v>
